--- a/order-grouping-progress.xlsx
+++ b/order-grouping-progress.xlsx
@@ -244,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -258,9 +258,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +715,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Order grouping  ·  2026-09-10</t>
+          <t>Order grouping  ·  2026-09-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +733,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Green = locked     Yellow = off (v1)     Graph values = examples     1 logic ✓  2 catalog fill ✓  3 Order Grouping Sorter  4 dry-run (no Input write until run)</t>
+          <t>Green = locked     Yellow = off (v1)     Graph values = examples except Hashim #038 Areeb pick-lists (Title Case; type has no gender; style is a product name)     1 logic ✓  2 catalog fill ✓  3 sorter ✓  4 Input write 2026-09-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -759,111 +756,81 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>PLAIN/PRINTED</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>1 / 2</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>plain</t>
+          <t>WAREHOUSE STOCK</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>own</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>P / R</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>S1</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>prime</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>dtf</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>readymade</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>printed ex.</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>or YYYY-MM-DD if future-fill</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>2nd / 3rd — also the Input folder</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>SKU plain/plainlg OR Plain Database/Packs match</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>or peeled channel e.g. fawad</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>design groups off</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>tag Amazon Prime Order</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>printed only; CL Printing Type</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>printed only; Customise</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>custom type off</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>product-finish</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>prime / non-prime</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>or SUPPLY ON DEMAND / IN HOUSE MANUFACTURE</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>personalised / ready made</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>testing: every --run is 1st Shift; production later S2 / S3</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>priority — today first, then prime, then as made</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>plain name</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Shift is the Input folder (1st Shift / 2nd Shift / 3rd Shift) and a filename slot (1st / 2nd / 3rd). Plain skips dtf / readymade / package-type (slots x). Adds supply-method and supplier when flags are 1. Packs vs Gildan = 30-chain (no pack colour). Amazon stays in own. MAS Clothing → fawad.</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Fixed batches: B40/B80/B100/B1050/B3700/…. Leftover: B1/B2/… (skip reserved). Filename keeps full 6 fields. Packing PIN uses B100-S1-1 Item 1 only. Shift folder stays 1st/2nd/3rd. Amazon stays in own. MAS Clothing → fawad (match only).</t>
         </is>
       </c>
       <c r="C6" s="2" t="n"/>
@@ -876,14 +843,14 @@
       <c r="J6" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>resend</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>filename is only:  resend     Exact tag 1014-ALL-RESEND only (not 1015 / 1016 / 1017). Wins even if ship-by is blank.</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>RESEND</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>filename is only:  RESEND     Exact tag 1014-ALL-RESEND only (not 1015 / 1016 / 1017). Wins even if ship-by is blank.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -896,14 +863,14 @@
       <c r="J8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>filename is only:  unmatched     No definite match. Floor handles this run; then investigate and tighten so the next run matches. Same order stays together.</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>UNMATCHED</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>filename is only:  UNMATCHED     No definite match. Floor handles this run; then investigate and tighten so the next run matches. Same order stays together.</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -928,37 +895,37 @@
       <c r="F11" s="3" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1. ShipStation
 awaiting_shipment only</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>2. Skip
 post-order-designs</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>3. Resend tag?
-→ file “resend”</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
+→ file “RESEND”</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>4. Blank ship-by
-→ unmatched</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
+→ today</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>5. Today/overdue first
 then future to fill cap</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>6. Folders 1st/2nd/3rd
 300/100/100 LINES</t>
@@ -966,15 +933,15 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>New process file when flag is 1</t>
         </is>
@@ -1017,360 +984,360 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>shift</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Filename slot 1st / 2nd / 3rd after today or YYYY-MM-DD. Also the Input folder (1st Shift = 300 lines, 2nd = 100, 3rd = 100)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Testing: filename field 1 S1 (after optional B-batch prefix) and Input 1st Shift every --run. Hashim #037: order volume &gt; 300 splits today vs later dates; do not dump into Shift 2/3. Blank ship-by → today (in awaiting_shipment → pull today; 2026-09-24). Production later: nth run = nth shift</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>plain / printed</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>Finish gate: SKU plain/plainlg → plain; else CL hit (after 1st dash) → printed; else Plain Database till-last-dash or Packs whole → plain; else unmatched</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Finish gate: SKU plain/plainlg → plain; else CL hit (after 1st dash, or whole SKU if no dash) → printed; else Plain Database till-last-dash or Packs whole → plain; else unmatched. Filename PLAIN or PRINTED</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>store / channel</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>MAS Clothing → process name fawad; more later; Amazon stays in own</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>MAS Clothing → fawad match (not a filename slot); Amazon stays in own</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>design group</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>per scenario, Design ID lists</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>prime</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>tag Amazon Prime Order (not CL Amazon Prime)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>printing method</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>CL Printing Type — DTF default; Sublimation = mugs</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>ready-made / customised</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>CL Customise</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>CL Customise. Mixed P vs R in one order: majority printed units; tie → readymade (not unmatched)</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>customisation type</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>CL Customisation Type (column empty; v1 slot x)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>print size</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>CL Print Size 1</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>print position</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>CL Print Positions</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>supply method</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Warehouse Stock = FOTL men/women/kids t-shirts only. In House Manufacture = SKU/GA contains iron on / ironon / iron-on / sticker (printed). Supplier On Demand = Gildan tees + everything else. Plain never in-house.</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>CL Warehouse Stock = FOTL tees in locked colour lists (Mens/Womens/Kids) plus Kids C800T/C8030T body colours. Filled 2026-09-23 (63,399 warehouse). Plain/Packs Warehouse Stock = all FOTL tees. In House = iron-on/sticker (printed). Else Supplier On Demand. Plain never in-house. Mixed supply-method → Supplier On Demand.</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>stock off / on-demand on</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>Supplier Name: BTC Activewear / Uneek Clothing / Absolute Apparels (babysuits C800T C8020T C8030T only)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>package type</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>packing PDF only (Large Letter / Parcel). Packs vs Gildan = 30-chain</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>Order Grouping Sorter (new app) writes Packing Input/{DD-MM-YYYY}/{1st|2nd|3rd} Shift/. Dry-run first: counts + process names, no Input write until run. Packs colour later.</t>
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Fixed batches first (B10…B8050, row order = priority), then plain B2000/B2100/B2200/B2500/B2600/… and printed leftover B1/B2/… skipping reserved. Hashim #037: orders &gt; 300 split today vs later. Testing: --run rewrites 1st Shift. Packing PIN: B100-S1-1 Item 1 (batch+shift only).</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1379,7 +1346,7 @@
       <c r="E30" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Then, if a bucket has 30+ units → another process file</t>
         </is>
@@ -1394,83 +1361,83 @@
       <c r="I32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Category (Areeb)</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>Product Type (Areeb)</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Product Style (Areeb)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Department (Areeb)</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>Brand / Brand Name</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>Size / Pack Size</t>
         </is>
       </c>
-      <c r="G33" s="20" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Colour</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="G34" s="25" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>30 both</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>30 both</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>30 both</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>have; packs later</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>Plain: every step 30     Printed: department always on, brand off, size on, colour 30</t>
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Fixed-batch FOTL / iron-on families skip the 30-chain (already their own file). Leftover Graph 30-chain (plain AND printed): every step 30. Packs skip colour.</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
@@ -1483,7 +1450,7 @@
       <c r="I35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>If a branch is not drawn all the way to colour, it still uses this chain (blank = save writing, not skip).</t>
         </is>
@@ -1498,9 +1465,9 @@
       <c r="I36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Printed in-house (iron-on or sticker, made here) uses the same 30-chain tail as warehouse-stock. Plain cannot be in-house. Mixed plain+printed order → whole order printed.</t>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Printed in-house (iron-on or sticker) uses the same 30-chain tail. Blank Brand/Colour on flag 30 stays in the parent (not unmatched). Plain cannot be in-house. Mixed plain+printed → whole order printed.</t>
         </is>
       </c>
       <c r="B37" s="2" t="n"/>
@@ -1513,9 +1480,9 @@
       <c r="I37" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>On each packing line</t>
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>On each packing line — batch, then process number, then item number</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -1529,9 +1496,9 @@
       <c r="J39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>Process today-1st-plain-own-…-1 Item 1     then     …-1 Item 2     then     …-2 Item 1</t>
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>B80-S1-1 Item 1     then     B80-S1-1 Item 2     then     B80-S1-2 Item 1</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
@@ -1545,9 +1512,9 @@
       <c r="J40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
-        <is>
-          <t>-1 / -2 = colour groups (3+ qty) first, then parts of 50 units. Item 1, 2 = lines. Same order keeps the same -N. Packs skip colour groups.</t>
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>PIN uses batch+shift only (B80-S1), not the full filename. Process number = colour 3+ then 50 units. Item number = line. Same order keeps the same process number. Packs skip colour groups.</t>
         </is>
       </c>
       <c r="B41" s="2" t="n"/>
@@ -1615,7 +1582,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Step 2 — catalog fill done (2026-09-08/09). Sorter reads; it does not overwrite.</t>
+          <t>Step 2 — catalog fill done (2026-09-08/09). CL Areeb squeezed refill 2026-09-16. Sorter reads; it does not overwrite.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1623,9 +1590,9 @@
       <c r="D1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>30-chain = Areeb columns. Do not overwrite PE Department. Packs colour later. Backup before any future fill.</t>
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>30-chain = Areeb columns. Do not overwrite PE Department. Packs colour later. Plain/Packs Areeb stay supplier copy. Backup before any future fill.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1655,361 +1622,361 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Customise (CL)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>have (Yes / blank)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>ready-made vs customised</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Printing Type (CL)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>FILLED — DTF / mug Sublimation</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>printed printing method</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Supply Method (all 3)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>FILLED — FOTL tees / iron-on+sticker / on-demand</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Warehouse Stock, In House Manufacture, Supplier On Demand</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Package Type / Package</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>CL 34%; Plain 100%; display</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>packing PDF; grouping off</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Supplier Name</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>FILLED — BTC Activewear / Uneek Clothing / Absolute babysuits</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>supplier split when flag 1</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Category (Areeb)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>FILLED on all 3</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>FILLED; pick-list #038 Title Case</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>≥30 new file</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Product Type (Areeb)</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>FILLED on all 3</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>FILLED; pick-list #038 no gender</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>≥30 new file</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Product Style (Areeb)</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>FILLED on all 3</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>FILLED; named product not code</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>≥30 new file</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Department (Areeb)</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>FILLED; CL = gender only</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>FILLED; CL = gender only (on list)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>plain 30 / printed 1</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Brand, Size, Colour</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>have (Packs: Brand Name + Pack Size; colour later)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>30+ files; colour 3+ qty → -N (not packs)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>30+ files; colour 3+ qty → -N (not packs). Same 30 on printed.</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Print Size 1</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>leave; fill later</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>print size split (v2)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Print Positions</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>have; split later</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>print position split (v2)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Amazon Prime (CL)</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>leave — not grouping</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>PO / inventory only</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>not grouping</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>customisation type</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>CL column empty; v1 off</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>name slot x in v1</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Plain Database.xlsx</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>grouping run is READ</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>till last dash → SKU</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>match</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Packs Database.xlsx</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>grouping run is READ</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>whole SKU → Channel Child SKU</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>match</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Step 3: Order Grouping Sorter. SKU keys: CL after 1st dash | Plain till last dash | Packs whole. Attrs: Packs→CL→Plain. Packs colour later.</t>
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: Order Grouping Sorter. SKU keys: CL after 1st dash (no dash → whole) | Plain till last dash | Packs whole. Attrs: Packs→CL→Plain. Packs colour later. Mixed supply → on-demand.</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -2055,7 +2022,7 @@
       <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>When you turn it on, process name slot = group-01, group-02…  Fill a scenario before a run.</t>
         </is>
@@ -2093,121 +2060,121 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>default (now)</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>CEO example</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>group-01</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>123LG, 245LG</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>sample only</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr"/>
-      <c r="B7" s="19" t="inlineStr"/>
-      <c r="C7" s="19" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr"/>
-      <c r="E7" s="19" t="inlineStr"/>
+      <c r="A7" s="18" t="inlineStr"/>
+      <c r="B7" s="18" t="inlineStr"/>
+      <c r="C7" s="18" t="inlineStr"/>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr"/>
-      <c r="C8" s="19" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="18" t="inlineStr"/>
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr"/>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="18" t="inlineStr"/>
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="18" t="inlineStr"/>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr"/>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="19" t="inlineStr"/>
-      <c r="D12" s="19" t="inlineStr"/>
-      <c r="E12" s="19" t="inlineStr"/>
+      <c r="A12" s="18" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr"/>
+      <c r="C12" s="18" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr"/>
+      <c r="E12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr"/>
-      <c r="B13" s="19" t="inlineStr"/>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr"/>
-      <c r="E13" s="19" t="inlineStr"/>
+      <c r="A13" s="18" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr"/>
+      <c r="C13" s="18" t="inlineStr"/>
+      <c r="D13" s="18" t="inlineStr"/>
+      <c r="E13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr"/>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="19" t="inlineStr"/>
-      <c r="D14" s="19" t="inlineStr"/>
-      <c r="E14" s="19" t="inlineStr"/>
+      <c r="A14" s="18" t="inlineStr"/>
+      <c r="B14" s="18" t="inlineStr"/>
+      <c r="C14" s="18" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr"/>
+      <c r="E14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr"/>
-      <c r="B15" s="19" t="inlineStr"/>
-      <c r="C15" s="19" t="inlineStr"/>
-      <c r="D15" s="19" t="inlineStr"/>
-      <c r="E15" s="19" t="inlineStr"/>
+      <c r="A15" s="18" t="inlineStr"/>
+      <c r="B15" s="18" t="inlineStr"/>
+      <c r="C15" s="18" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr"/>
+      <c r="E15" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/order-grouping-progress.xlsx
+++ b/order-grouping-progress.xlsx
@@ -715,7 +715,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Order grouping  ·  2026-09-29</t>
+          <t>Order grouping  ·  2026-09-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>

--- a/order-grouping-progress.xlsx
+++ b/order-grouping-progress.xlsx
@@ -715,7 +715,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Order grouping  ·  2026-09-30</t>
+          <t>Order grouping  ·  2026-10-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
